--- a/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
+++ b/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Sector_selection" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Year_selection" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Rounding_thresholds" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Timeseries_selection" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="Fuels">#REF!</definedName>
@@ -2109,6 +2110,272 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Timeseries</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Timeseries selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TS_COOL_LOW</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TS_HEAT_HIGH</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TS_HEAT_LOW</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TS_HP_AIRSOURCE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TS_HP_GROUNDSOURCE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TS_HYDRO_ROR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TS_LOAD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TS_MOBILITY_PSNG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TS_POWER_BEVS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TS_POWER_BUILDINGS_COOLING</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TS_POWER_BUILDINGS_HEAT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TS_POWER_DATACENTER</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TS_POWER_HYDROGEN</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TS_PV_AVG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TS_PV_INF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TS_PV_OPT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TS_PV_ROOFTOP</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TS_PV_TRA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TS_WIND_OFFSHORE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TS_WIND_OFFSHORE_DEEP</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TS_WIND_OFFSHORE_SHALLOW</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TS_WIND_ONSHORE_AVG</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TS_WIND_ONSHORE_INF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TS_WIND_ONSHORE_OPT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
+++ b/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
@@ -2382,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3933,7 +3933,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HLI_Heatpump</t>
+          <t>P_EGS_R1</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3943,7 +3943,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>X_Convert_Power</t>
+          <t>P_EGS_R2</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3953,7 +3953,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Z_Import_Biomass</t>
+          <t>P_EGS_R3</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3963,10 +3963,50 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>P_EGS_R4</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HLI_Heatpump</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>X_Convert_Power</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Z_Import_Biomass</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>Z_Import_Lignite</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B162" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
+++ b/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
@@ -2382,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B162"/>
+  <dimension ref="A1:B163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3313,7 +3313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>P_Geothermal</t>
+          <t>P_Gas_Steam</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3323,7 +3323,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>P_H2_OCGT</t>
+          <t>P_Geothermal</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3333,7 +3333,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>P_Hydro_Reservoir</t>
+          <t>P_H2_OCGT</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3343,7 +3343,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>P_Hydro_RoR</t>
+          <t>P_Hydro_Reservoir</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3353,7 +3353,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>P_Nuclear</t>
+          <t>P_Hydro_RoR</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3363,7 +3363,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>P_Ocean</t>
+          <t>P_Nuclear</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3373,7 +3373,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>P_Oil</t>
+          <t>P_Ocean</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3383,7 +3383,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>P_PV_Rooftop_Commercial</t>
+          <t>P_Oil</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3393,7 +3393,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>P_PV_Rooftop_Residential</t>
+          <t>P_PV_Rooftop_Commercial</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3403,7 +3403,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Avg</t>
+          <t>P_PV_Rooftop_Residential</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -3413,7 +3413,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Inf</t>
+          <t>P_PV_Utility_Avg</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3423,7 +3423,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Opt</t>
+          <t>P_PV_Utility_Inf</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3433,7 +3433,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Tracking</t>
+          <t>P_PV_Utility_Opt</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3443,7 +3443,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Deep</t>
+          <t>P_PV_Utility_Tracking</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3453,7 +3453,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Shallow</t>
+          <t>P_Wind_Offshore_Deep</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3463,7 +3463,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Transitional</t>
+          <t>P_Wind_Offshore_Shallow</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3473,7 +3473,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>P_Wind_Onshore_Avg</t>
+          <t>P_Wind_Offshore_Transitional</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3483,7 +3483,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>P_Wind_Onshore_Inf</t>
+          <t>P_Wind_Onshore_Avg</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3493,17 +3493,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>P_Wind_Onshore_Inf</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>P_Wind_Onshore_Opt</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>PSNG_Air_Bio</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3513,7 +3513,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Air_Conv</t>
+          <t>PSNG_Air_Bio</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3523,7 +3523,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Air_H2</t>
+          <t>PSNG_Air_Conv</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3533,7 +3533,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Rail_Conv</t>
+          <t>PSNG_Air_H2</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3543,7 +3543,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Rail_Electric</t>
+          <t>PSNG_Rail_Conv</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3553,7 +3553,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_BEV</t>
+          <t>PSNG_Rail_Electric</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3563,7 +3563,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_H2</t>
+          <t>PSNG_Road_BEV</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3573,7 +3573,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_ICE</t>
+          <t>PSNG_Road_H2</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3583,7 +3583,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_LNG</t>
+          <t>PSNG_Road_ICE</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3593,17 +3593,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>PSNG_Road_LNG</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>PSNG_Road_PHEV</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>R_Biogas</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3613,7 +3613,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R_Coal_Hardcoal</t>
+          <t>R_Biogas</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3623,7 +3623,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R_Coal_Lignite</t>
+          <t>R_Coal_Hardcoal</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3633,7 +3633,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R_Gas</t>
+          <t>R_Coal_Lignite</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3643,7 +3643,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R_Grass</t>
+          <t>R_Gas</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3653,7 +3653,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R_Nuclear</t>
+          <t>R_Grass</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3663,7 +3663,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R_Oil</t>
+          <t>R_Nuclear</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3673,7 +3673,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R_Paper_Cardboard</t>
+          <t>R_Oil</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3683,7 +3683,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R_Residues</t>
+          <t>R_Paper_Cardboard</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3693,7 +3693,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R_Roundwood</t>
+          <t>R_Residues</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3703,7 +3703,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R_Waste</t>
+          <t>R_Roundwood</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3713,7 +3713,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R_Wood</t>
+          <t>R_Waste</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3723,7 +3723,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>X_Alkaline_Electrolysis</t>
+          <t>R_Wood</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3733,7 +3733,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>X_ATR_CCS</t>
+          <t>X_Alkaline_Electrolysis</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3743,7 +3743,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>X_Biofuel</t>
+          <t>X_ATR_CCS</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3753,17 +3753,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>X_Biofuel</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>X_Convert_HD</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>X_DAC_HT</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3773,27 +3773,27 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>X_DAC_HT</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
           <t>X_DAC_LT</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>X_Electrolysis</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>X_Gasifier</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3803,17 +3803,17 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>X_Gasifier</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
           <t>X_Liquifier</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>X_Methanation</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3823,7 +3823,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>X_PEM_Electrolysis</t>
+          <t>X_Methanation</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3833,7 +3833,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>X_Powerfuel</t>
+          <t>X_PEM_Electrolysis</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3843,7 +3843,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>X_SMR</t>
+          <t>X_Powerfuel</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3853,7 +3853,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>X_SOEC_Electrolysis</t>
+          <t>X_SMR</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3863,7 +3863,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Z_ETS_Buy</t>
+          <t>X_SOEC_Electrolysis</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3873,7 +3873,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Z_ETS_Sell</t>
+          <t>Z_ETS_Buy</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3883,27 +3883,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
+          <t>Z_ETS_Sell</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>Z_Import_Gas</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Z_Import_H2</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Z_Import_Hardcoal</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3913,7 +3913,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Z_Import_LNG</t>
+          <t>Z_Import_Hardcoal</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3923,7 +3923,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Z_Import_Oil</t>
+          <t>Z_Import_LNG</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3933,7 +3933,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>P_EGS_R1</t>
+          <t>Z_Import_Oil</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3943,7 +3943,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>P_EGS_R2</t>
+          <t>P_EGS_R1</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3953,7 +3953,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>P_EGS_R3</t>
+          <t>P_EGS_R2</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3963,7 +3963,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>P_EGS_R4</t>
+          <t>P_EGS_R3</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3973,7 +3973,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>HLI_Heatpump</t>
+          <t>P_EGS_R4</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3983,7 +3983,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>X_Convert_Power</t>
+          <t>HLI_Heatpump</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3993,7 +3993,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Z_Import_Biomass</t>
+          <t>X_Convert_Power</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4003,10 +4003,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>Z_Import_Biomass</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
           <t>Z_Import_Lignite</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B163" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
+++ b/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
@@ -2382,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B163"/>
+  <dimension ref="A1:B165"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4017,6 +4017,26 @@
         </is>
       </c>
       <c r="B163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>P_Nuclear_SMR</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>P_Gas_CCGT_Residual</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
+++ b/Conversion Script/Set_filter_file_NorthAmerica_allFuels.xlsx
@@ -2382,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3313,7 +3313,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>P_Gas_Steam</t>
+          <t>P_Geothermal</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3323,7 +3323,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>P_Geothermal</t>
+          <t>P_H2_OCGT</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3333,7 +3333,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>P_H2_OCGT</t>
+          <t>P_Hydro_Reservoir</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3343,7 +3343,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>P_Hydro_Reservoir</t>
+          <t>P_Hydro_RoR</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3353,7 +3353,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>P_Hydro_RoR</t>
+          <t>P_Nuclear</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3363,7 +3363,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>P_Nuclear</t>
+          <t>P_Ocean</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3373,7 +3373,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>P_Ocean</t>
+          <t>P_Oil</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3383,7 +3383,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>P_Oil</t>
+          <t>P_PV_Rooftop_Commercial</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3393,7 +3393,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>P_PV_Rooftop_Commercial</t>
+          <t>P_PV_Rooftop_Residential</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3403,7 +3403,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>P_PV_Rooftop_Residential</t>
+          <t>P_PV_Utility_Avg</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -3413,7 +3413,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Avg</t>
+          <t>P_PV_Utility_Inf</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3423,7 +3423,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Inf</t>
+          <t>P_PV_Utility_Opt</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3433,7 +3433,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Opt</t>
+          <t>P_PV_Utility_Tracking</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3443,7 +3443,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>P_PV_Utility_Tracking</t>
+          <t>P_Wind_Offshore_Deep</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3453,7 +3453,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Deep</t>
+          <t>P_Wind_Offshore_Shallow</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3463,7 +3463,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Shallow</t>
+          <t>P_Wind_Offshore_Transitional</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3473,7 +3473,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>P_Wind_Offshore_Transitional</t>
+          <t>P_Wind_Onshore_Avg</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3483,7 +3483,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>P_Wind_Onshore_Avg</t>
+          <t>P_Wind_Onshore_Inf</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3493,7 +3493,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>P_Wind_Onshore_Inf</t>
+          <t>P_Wind_Onshore_Opt</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3501,9 +3501,9 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>P_Wind_Onshore_Opt</t>
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>PSNG_Air_Bio</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3513,7 +3513,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Air_Bio</t>
+          <t>PSNG_Air_Conv</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3523,7 +3523,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Air_Conv</t>
+          <t>PSNG_Air_H2</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3533,7 +3533,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Air_H2</t>
+          <t>PSNG_Rail_Conv</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -3543,7 +3543,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Rail_Conv</t>
+          <t>PSNG_Rail_Electric</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -3553,7 +3553,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Rail_Electric</t>
+          <t>PSNG_Road_BEV</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -3563,7 +3563,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_BEV</t>
+          <t>PSNG_Road_H2</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -3573,7 +3573,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_H2</t>
+          <t>PSNG_Road_ICE</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3583,7 +3583,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_ICE</t>
+          <t>PSNG_Road_LNG</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -3593,7 +3593,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PSNG_Road_LNG</t>
+          <t>PSNG_Road_PHEV</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3601,9 +3601,9 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>PSNG_Road_PHEV</t>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>R_Biogas</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -3613,7 +3613,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R_Biogas</t>
+          <t>R_Coal_Hardcoal</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -3623,7 +3623,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R_Coal_Hardcoal</t>
+          <t>R_Coal_Lignite</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -3633,7 +3633,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R_Coal_Lignite</t>
+          <t>R_Gas</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -3643,7 +3643,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R_Gas</t>
+          <t>R_Grass</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3653,7 +3653,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R_Grass</t>
+          <t>R_Nuclear</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -3663,7 +3663,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R_Nuclear</t>
+          <t>R_Oil</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3673,7 +3673,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R_Oil</t>
+          <t>R_Paper_Cardboard</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3683,7 +3683,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R_Paper_Cardboard</t>
+          <t>R_Residues</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -3693,7 +3693,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R_Residues</t>
+          <t>R_Roundwood</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3703,7 +3703,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R_Roundwood</t>
+          <t>R_Waste</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -3713,7 +3713,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R_Waste</t>
+          <t>R_Wood</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3723,7 +3723,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R_Wood</t>
+          <t>X_Alkaline_Electrolysis</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3733,7 +3733,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>X_Alkaline_Electrolysis</t>
+          <t>X_ATR_CCS</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -3743,7 +3743,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>X_ATR_CCS</t>
+          <t>X_Biofuel</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -3753,7 +3753,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>X_Biofuel</t>
+          <t>X_Convert_HD</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -3761,9 +3761,9 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>X_Convert_HD</t>
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>X_DAC_HT</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -3773,7 +3773,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>X_DAC_HT</t>
+          <t>X_DAC_LT</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3781,9 +3781,9 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>X_DAC_LT</t>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>X_Electrolysis</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -3791,9 +3791,9 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>X_Electrolysis</t>
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>X_Gasifier</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -3803,7 +3803,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>X_Gasifier</t>
+          <t>X_Liquifier</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -3811,9 +3811,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>X_Liquifier</t>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>X_Methanation</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -3823,7 +3823,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>X_Methanation</t>
+          <t>X_PEM_Electrolysis</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -3833,7 +3833,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>X_PEM_Electrolysis</t>
+          <t>X_Powerfuel</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -3843,7 +3843,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>X_Powerfuel</t>
+          <t>X_SMR</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3853,7 +3853,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>X_SMR</t>
+          <t>X_SOEC_Electrolysis</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -3863,7 +3863,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>X_SOEC_Electrolysis</t>
+          <t>Z_ETS_Buy</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -3873,7 +3873,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Z_ETS_Buy</t>
+          <t>Z_ETS_Sell</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -3883,7 +3883,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Z_ETS_Sell</t>
+          <t>Z_Import_Gas</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -3891,9 +3891,9 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Z_Import_Gas</t>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Z_Import_H2</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -3901,9 +3901,9 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Z_Import_H2</t>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Z_Import_Hardcoal</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3913,7 +3913,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Z_Import_Hardcoal</t>
+          <t>Z_Import_LNG</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -3923,7 +3923,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Z_Import_LNG</t>
+          <t>Z_Import_Oil</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3933,7 +3933,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Z_Import_Oil</t>
+          <t>P_EGS_R1</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -3943,7 +3943,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>P_EGS_R1</t>
+          <t>P_EGS_R2</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -3953,7 +3953,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>P_EGS_R2</t>
+          <t>P_EGS_R3</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3963,7 +3963,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>P_EGS_R3</t>
+          <t>P_EGS_R4</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -3973,7 +3973,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>P_EGS_R4</t>
+          <t>HLI_Heatpump</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -3983,7 +3983,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>HLI_Heatpump</t>
+          <t>X_Convert_Power</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -3993,7 +3993,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>X_Convert_Power</t>
+          <t>Z_Import_Biomass</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4003,7 +4003,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Z_Import_Biomass</t>
+          <t>Z_Import_Lignite</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4013,7 +4013,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Z_Import_Lignite</t>
+          <t>P_Gas_Steam</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4037,6 +4037,16 @@
         </is>
       </c>
       <c r="B165" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>P_SOFC</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
         <v>1</v>
       </c>
     </row>
